--- a/rulebook-examples/legacy-runner/execution-substrates/xlsx/rulebook.xlsx
+++ b/rulebook-examples/legacy-runner/execution-substrates/xlsx/rulebook.xlsx
@@ -159,12 +159,12 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the customers.</t>
+        <t>Identifier for the customer.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Thec ustomers email address</t>
+        <t>The customer's email address</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -521,7 +521,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>jane-smith-email-com</t>
+          <t>bob-gmail-com</t>
         </is>
       </c>
       <c r="B2" s="3">
@@ -530,12 +530,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>bob@gmail.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>john-doe-email-com</t>
+          <t>jimmy-gmail-com</t>
         </is>
       </c>
       <c r="B3" s="3">
@@ -560,7 +560,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>jimmy@gmail.com</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>emily-jones-email-com</t>
+          <t>mary-gmail-com</t>
         </is>
       </c>
       <c r="B4" s="3">
@@ -590,7 +590,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>mary@gmail.com</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
